--- a/web/files/港岛-香港仔及鸭脷洲-逸南.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-逸南.xlsx
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-03-31</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2022-02-21</t>
+          <t>2022-02-22</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-23</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2021-06-23</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2022-07-12</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2022-01-06</t>
+          <t>2022-01-07</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2021-12-28</t>
+          <t>2021-12-29</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2021-06-18</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2021-06-23</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2022-08-04</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2021-06-27</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2021-08-08</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-08-12</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2021-06-27</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2021-10-19</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
+          <t>2021-12-24</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2021-11-25</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2022-02-23</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2021-05-29</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9703,7 +9703,7 @@
           <t>A | 264呎 (1房)
 $736万
 $27,897/呎
-(23年-03月-28日)</t>
+(23年-03月-29日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -9743,7 +9743,7 @@
           <t>F | 264呎 (1房)
 $716万
 $27,125/呎
-(23年-03月-30日)</t>
+(23年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9758,7 @@
           <t>A | 264呎 (1房)
 $726万
 $27,506/呎
-(21年-11月-09日)</t>
+(21年-11月-10日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -9813,7 +9813,7 @@
           <t>A | 264呎 (1房)
 $720万
 $27,274/呎
-(23年-05月-07日)</t>
+(23年-05月-08日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -9868,7 +9868,7 @@
           <t>A | 264呎 (1房)
 $714万
 $27,039/呎
-(21年-08月-16日)</t>
+(21年-08月-17日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -9876,7 +9876,7 @@
           <t>B | 186呎 (开放式)
 $515万
 $27,700/呎
-(21年-09月-22日)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -9892,7 +9892,7 @@
           <t>D | 183呎 (开放式)
 $492万
 $26,910/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -9908,7 +9908,7 @@
           <t>F | 264呎 (1房)
 $672万
 $25,451/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
           <t>A | 264呎 (1房)
 $708万
 $26,808/呎
-(21年-06月-29日)</t>
+(21年-06月-30日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -9931,7 +9931,7 @@
           <t>B | 186呎 (开放式)
 $512万
 $27,538/呎
-(22年-02月-21日)</t>
+(22年-02月-22日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -9978,7 +9978,7 @@
           <t>A | 264呎 (1房)
 $704万
 $26,655/呎
-(21年-07月-01日)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -9986,7 +9986,7 @@
           <t>B | 186呎 (开放式)
 $509万
 $27,381/呎
-(21年-06月-23日)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -10010,7 +10010,7 @@
           <t>E | 186呎 (开放式)
 $493万
 $26,492/呎
-(21年-07月-22日)</t>
+(21年-07月-23日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -10018,7 +10018,7 @@
           <t>F | 264呎 (1房)
 $662万
 $25,092/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
           <t>A | 264呎 (1房)
 $707万
 $26,780/呎
-(21年-09月-22日)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -10041,7 +10041,7 @@
           <t>B | 186呎 (开放式)
 $539万
 $28,957/呎
-(21年-08月-16日)</t>
+(21年-08月-17日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -10073,7 +10073,7 @@
           <t>F | 264呎 (1房)
 $666万
 $25,215/呎
-(21年-06月-15日)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
           <t>A | 264呎 (1房)
 $678万
 $25,700/呎
-(21年-06月-22日)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -10096,7 +10096,7 @@
           <t>B | 186呎 (开放式)
 $530万
 $28,497/呎
-(21年-06月-22日)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -10104,7 +10104,7 @@
           <t>C | 183呎 (开放式)
 $486万
 $26,582/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -10120,7 +10120,7 @@
           <t>E | 186呎 (开放式)
 $487万
 $26,184/呎
-(21年-06月-24日)</t>
+(21年-06月-25日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -10128,7 +10128,7 @@
           <t>F | 264呎 (1房)
 $655万
 $24,803/呎
-(21年-06月-28日)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
           <t>A | 264呎 (1房)
 $728万
 $27,585/呎
-(21年-06月-24日)</t>
+(21年-06月-25日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -10151,7 +10151,7 @@
           <t>B | 186呎 (开放式)
 $506万
 $27,182/呎
-(21年-12月-19日)</t>
+(21年-12月-20日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -10175,7 +10175,7 @@
           <t>E | 186呎 (开放式)
 $484万
 $26,037/呎
-(22年-07月-11日)</t>
+(22年-07月-12日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -10183,7 +10183,7 @@
           <t>F | 264呎 (1房)
 $675万
 $25,567/呎
-(21年-09月-23日)</t>
+(21年-09月-24日)</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10198,7 @@
           <t>A | 264呎 (1房)
 $687万
 $26,035/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -10206,7 +10206,7 @@
           <t>B | 186呎 (开放式)
 $497万
 $26,734/呎
-(22年-01月-06日)</t>
+(22年-01月-07日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -10238,7 +10238,7 @@
           <t>F | 264呎 (1房)
 $655万
 $24,808/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -10253,7 +10253,7 @@
           <t>A | 264呎 (1房)
 $666万
 $25,245/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -10261,7 +10261,7 @@
           <t>B | 186呎 (开放式)
 $500万
 $26,855/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -10269,7 +10269,7 @@
           <t>C | 183呎 (开放式)
 $504万
 $27,514/呎
-(21年-06月-22日)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -10277,7 +10277,7 @@
           <t>D | 183呎 (开放式)
 $473万
 $25,837/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -10293,7 +10293,7 @@
           <t>F | 264呎 (1房)
 $667万
 $25,279/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
           <t>A | 264呎 (1房)
 $698万
 $26,426/呎
-(21年-06月-17日)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -10316,7 +10316,7 @@
           <t>B | 186呎 (开放式)
 $523万
 $28,097/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -10324,7 +10324,7 @@
           <t>C | 183呎 (开放式)
 $506万
 $27,628/呎
-(21年-12月-28日)</t>
+(21年-12月-29日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -10332,7 +10332,7 @@
           <t>D | 183呎 (开放式)
 $470万
 $25,683/呎
-(21年-06月-29日)</t>
+(21年-06月-30日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -10340,7 +10340,7 @@
           <t>E | 186呎 (开放式)
 $476万
 $25,582/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -10363,7 +10363,7 @@
           <t>A | 242呎 (1房)
 $663万
 $27,401/呎
-(21年-10月-06日)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -10371,7 +10371,7 @@
           <t>B | 186呎 (开放式)
 $493万
 $26,528/呎
-(21年-09月-29日)</t>
+(21年-09月-30日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -10379,7 +10379,7 @@
           <t>C | 183呎 (开放式)
 $477万
 $26,091/呎
-(21年-10月-10日)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -10387,7 +10387,7 @@
           <t>D | 183呎 (开放式)
 $467万
 $25,534/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -10395,7 +10395,7 @@
           <t>E | 186呎 (开放式)
 $473万
 $25,431/呎
-(22年-08月-04日)</t>
+(22年-08月-05日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -10403,7 +10403,7 @@
           <t>F | 242呎 (1房)
 $652万
 $26,930/呎
-(21年-06月-23日)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
           <t>A | 242呎 (1房)
 $636万
 $26,281/呎
-(21年-06月-15日)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -10426,7 +10426,7 @@
           <t>B | 186呎 (开放式)
 $485万
 $26,088/呎
-(21年-08月-08日)</t>
+(21年-08月-09日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -10434,7 +10434,7 @@
           <t>C | 183呎 (开放式)
 $470万
 $25,663/呎
-(21年-06月-15日)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -10442,7 +10442,7 @@
           <t>D | 183呎 (开放式)
 $464万
 $25,380/呎
-(21年-06月-27日)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -10450,7 +10450,7 @@
           <t>E | 186呎 (开放式)
 $468万
 $25,153/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -10458,7 +10458,7 @@
           <t>F | 242呎 (1房)
 $647万
 $26,755/呎
-(21年-06月-16日)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -10473,7 +10473,7 @@
           <t>A | 242呎 (1房)
 $639万
 $26,396/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -10481,7 +10481,7 @@
           <t>B | 186呎 (开放式)
 $481万
 $25,845/呎
-(21年-10月-07日)</t>
+(21年-10月-08日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -10489,7 +10489,7 @@
           <t>C | 183呎 (开放式)
 $470万
 $25,707/呎
-(21年-08月-17日)</t>
+(21年-08月-18日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -10497,7 +10497,7 @@
           <t>D | 183呎 (开放式)
 $485万
 $26,487/呎
-(21年-08月-11日)</t>
+(21年-08月-12日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -10513,7 +10513,7 @@
           <t>F | 242呎 (1房)
 $611万
 $25,236/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -10528,7 +10528,7 @@
           <t>A | 242呎 (1房)
 $626万
 $25,869/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -10536,7 +10536,7 @@
           <t>B | 186呎 (开放式)
 $475万
 $25,522/呎
-(21年-06月-28日)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -10544,7 +10544,7 @@
           <t>C | 183呎 (开放式)
 $465万
 $25,396/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -10552,7 +10552,7 @@
           <t>D | 183呎 (开放式)
 $479万
 $26,167/呎
-(21年-06月-27日)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -10560,7 +10560,7 @@
           <t>E | 186呎 (开放式)
 $461万
 $24,779/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -10568,7 +10568,7 @@
           <t>F | 242呎 (1房)
 $639万
 $26,407/呎
-(21年-06月-28日)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10583,7 @@
           <t>A | 242呎 (1房)
 $638万
 $26,347/呎
-(21年-12月-23日)</t>
+(21年-12月-24日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -10591,7 +10591,7 @@
           <t>B | 186呎 (开放式)
 $470万
 $25,284/呎
-(21年-10月-19日)</t>
+(21年-10月-20日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -10599,7 +10599,7 @@
           <t>C | 183呎 (开放式)
 $456万
 $24,897/呎
-(21年-10月-26日)</t>
+(21年-10月-27日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -10623,7 +10623,7 @@
           <t>F | 242呎 (1房)
 $635万
 $26,231/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -10638,7 +10638,7 @@
           <t>A | 242呎 (1房)
 $636万
 $26,262/呎
-(22年-02月-23日)</t>
+(22年-02月-24日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -10646,7 +10646,7 @@
           <t>B | 186呎 (开放式)
 $494万
 $26,544/呎
-(21年-11月-25日)</t>
+(21年-11月-26日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -10678,7 +10678,7 @@
           <t>F | 242呎 (1房)
 $601万
 $24,825/呎
-(21年-06月-28日)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -10693,7 +10693,7 @@
           <t>A | 242呎 (1房)
 $623万
 $25,729/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -10701,7 +10701,7 @@
           <t>B | 186呎 (开放式)
 $471万
 $25,308/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -10709,7 +10709,7 @@
           <t>C | 183呎 (开放式)
 $451万
 $24,671/呎
-(21年-06月-22日)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -10717,7 +10717,7 @@
           <t>D | 183呎 (开放式)
 $451万
 $24,643/呎
-(21年-06月-28日)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -10725,7 +10725,7 @@
           <t>E | 186呎 (开放式)
 $450万
 $24,215/呎
-(21年-06月-22日)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -10733,7 +10733,7 @@
           <t>F | 242呎 (1房)
 $596万
 $24,642/呎
-(21年-06月-22日)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10748,7 @@
           <t>A | 242呎 (1房)
 $612万
 $25,291/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -10764,7 +10764,7 @@
           <t>C | 183呎 (开放式)
 $473万
 $25,821/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -10772,7 +10772,7 @@
           <t>D | 183呎 (开放式)
 $443万
 $24,235/呎
-(21年-06月-22日)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -10780,7 +10780,7 @@
           <t>E | 186呎 (开放式)
 $464万
 $24,963/呎
-(21年-06月-15日)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -10788,7 +10788,7 @@
           <t>F | 242呎 (1房)
 $592万
 $24,479/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10803,7 @@
           <t>A | 242呎 (1房)
 $612万
 $25,305/呎
-(21年-07月-01日)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -10819,7 +10819,7 @@
           <t>C | 183呎 (开放式)
 $444万
 $24,286/呎
-(21年-08月-16日)</t>
+(21年-08月-17日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -10827,7 +10827,7 @@
           <t>D | 183呎 (开放式)
 $439万
 $24,003/呎
-(21年-10月-03日)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -10835,7 +10835,7 @@
           <t>E | 186呎 (开放式)
 $444万
 $23,857/呎
-(21年-09月-22日)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -10843,7 +10843,7 @@
           <t>F | 242呎 (1房)
 $593万
 $24,488/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10858,7 @@
           <t>A | 242呎 (1房)
 $600万
 $24,786/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -10866,7 +10866,7 @@
           <t>B | 186呎 (开放式)
 $452万
 $24,314/呎
-(21年-10月-10日)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -10874,7 +10874,7 @@
           <t>C | 183呎 (开放式)
 $439万
 $23,983/呎
-(21年-06月-16日)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -10882,7 +10882,7 @@
           <t>D | 183呎 (开放式)
 $438万
 $23,947/呎
-(21年-11月-11日)</t>
+(21年-11月-12日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -10890,7 +10890,7 @@
           <t>E | 186呎 (开放式)
 $428万
 $22,990/呎
-(21年-05月-29日)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -10898,7 +10898,7 @@
           <t>F | 242呎 (1房)
 $581万
 $23,997/呎
-(21年-06月-10日)</t>
+(21年-06月-11日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-逸南.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-逸南.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,6 +116,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
@@ -207,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -266,16 +272,19 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,7 +776,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -777,12 +786,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -792,12 +801,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -807,7 +816,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -837,7 +846,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -847,12 +856,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -862,12 +871,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -877,7 +886,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -907,7 +916,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -917,12 +926,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -932,12 +941,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -947,7 +956,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1126,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1127,12 +1136,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1142,12 +1151,12 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1157,7 +1166,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9563,14 +9572,14 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
           <t>91</t>
@@ -9583,7 +9592,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -9633,17 +9642,17 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 300呎 (1房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 300呎 (1房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>B | 300呎 (1房)
--
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr"/>
@@ -9660,12 +9669,12 @@
       <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 334呎 (1房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 183呎 (开放式)
 -
@@ -9673,7 +9682,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 -
@@ -9684,9 +9693,9 @@
       <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 334呎 (1房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr"/>
@@ -9698,7 +9707,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 264呎 (1房)
 $736万
@@ -9706,7 +9715,7 @@
 (23年-03月-29日)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 -
@@ -9714,7 +9723,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 -
@@ -9722,7 +9731,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 -
@@ -9730,7 +9739,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 -
@@ -9738,7 +9747,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>F | 264呎 (1房)
 $716万
@@ -9753,7 +9762,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 264呎 (1房)
 $726万
@@ -9761,7 +9770,7 @@
 (21年-11月-10日)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 -
@@ -9769,7 +9778,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 -
@@ -9777,7 +9786,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 -
@@ -9785,7 +9794,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 -
@@ -9793,7 +9802,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>F | 264呎 (1房)
 $749万
@@ -9808,7 +9817,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 264呎 (1房)
 $720万
@@ -9816,7 +9825,7 @@
 (23年-05月-08日)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 -
@@ -9824,7 +9833,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 -
@@ -9832,7 +9841,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 -
@@ -9840,7 +9849,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 -
@@ -9848,7 +9857,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t>F | 264呎 (1房)
 $741万
@@ -9863,7 +9872,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 264呎 (1房)
 $714万
@@ -9871,7 +9880,7 @@
 (21年-08月-17日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $515万
@@ -9879,7 +9888,7 @@
 (21年-09月-23日)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $529万
@@ -9887,7 +9896,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $492万
@@ -9895,7 +9904,7 @@
 (23年-04月-28日)</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $530万
@@ -9903,7 +9912,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>F | 264呎 (1房)
 $672万
@@ -9918,7 +9927,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 264呎 (1房)
 $708万
@@ -9926,7 +9935,7 @@
 (21年-06月-30日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $512万
@@ -9934,7 +9943,7 @@
 (22年-02月-22日)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 -
@@ -9942,7 +9951,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 -
@@ -9950,7 +9959,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $527万
@@ -9958,7 +9967,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>F | 264呎 (1房)
 $726万
@@ -9973,7 +9982,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 264呎 (1房)
 $704万
@@ -9981,7 +9990,7 @@
 (21年-07月-02日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $509万
@@ -9989,7 +9998,7 @@
 (21年-06月-24日)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $524万
@@ -9997,7 +10006,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $518万
@@ -10005,7 +10014,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $493万
@@ -10013,7 +10022,7 @@
 (21年-07月-23日)</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>F | 264呎 (1房)
 $662万
@@ -10028,7 +10037,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 264呎 (1房)
 $707万
@@ -10036,7 +10045,7 @@
 (21年-09月-23日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $539万
@@ -10044,7 +10053,7 @@
 (21年-08月-17日)</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $520万
@@ -10052,7 +10061,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $515万
@@ -10060,7 +10069,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $521万
@@ -10068,7 +10077,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>F | 264呎 (1房)
 $666万
@@ -10083,7 +10092,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 264呎 (1房)
 $678万
@@ -10091,7 +10100,7 @@
 (21年-06月-23日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $530万
@@ -10099,7 +10108,7 @@
 (21年-06月-23日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $486万
@@ -10107,7 +10116,7 @@
 (21年-09月-27日)</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $512万
@@ -10115,7 +10124,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $487万
@@ -10123,7 +10132,7 @@
 (21年-06月-25日)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>F | 264呎 (1房)
 $655万
@@ -10138,7 +10147,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 264呎 (1房)
 $728万
@@ -10146,7 +10155,7 @@
 (21年-06月-25日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $506万
@@ -10154,7 +10163,7 @@
 (21年-12月-20日)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $514万
@@ -10162,7 +10171,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $509万
@@ -10170,7 +10179,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $484万
@@ -10178,7 +10187,7 @@
 (22年-07月-12日)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>F | 264呎 (1房)
 $675万
@@ -10193,7 +10202,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 264呎 (1房)
 $687万
@@ -10201,7 +10210,7 @@
 (21年-06月-21日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $497万
@@ -10209,7 +10218,7 @@
 (22年-01月-07日)</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 -
@@ -10217,7 +10226,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 -
@@ -10225,7 +10234,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 -
@@ -10233,7 +10242,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 264呎 (1房)
 $655万
@@ -10248,7 +10257,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 264呎 (1房)
 $666万
@@ -10256,7 +10265,7 @@
 (21年-06月-21日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $500万
@@ -10264,7 +10273,7 @@
 (21年-06月-22日)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $504万
@@ -10272,7 +10281,7 @@
 (21年-06月-23日)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $473万
@@ -10280,7 +10289,7 @@
 (21年-06月-22日)</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $509万
@@ -10288,7 +10297,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>F | 264呎 (1房)
 $667万
@@ -10303,7 +10312,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 264呎 (1房)
 $698万
@@ -10311,7 +10320,7 @@
 (21年-06月-18日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $523万
@@ -10319,7 +10328,7 @@
 (21年-06月-21日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $506万
@@ -10327,7 +10336,7 @@
 (21年-12月-29日)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $470万
@@ -10335,7 +10344,7 @@
 (21年-06月-30日)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $476万
@@ -10343,7 +10352,7 @@
 (21年-06月-22日)</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G18" s="24" t="inlineStr">
         <is>
           <t>F | 264呎 (1房)
 $705万
@@ -10358,7 +10367,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 242呎 (1房)
 $663万
@@ -10366,7 +10375,7 @@
 (21年-10月-07日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $493万
@@ -10374,7 +10383,7 @@
 (21年-09月-30日)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $477万
@@ -10382,7 +10391,7 @@
 (21年-10月-11日)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $467万
@@ -10390,7 +10399,7 @@
 (21年-09月-27日)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $473万
@@ -10398,7 +10407,7 @@
 (22年-08月-05日)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>F | 242呎 (1房)
 $652万
@@ -10413,7 +10422,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 242呎 (1房)
 $636万
@@ -10421,7 +10430,7 @@
 (21年-06月-16日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $485万
@@ -10429,7 +10438,7 @@
 (21年-08月-09日)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $470万
@@ -10437,7 +10446,7 @@
 (21年-06月-16日)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $464万
@@ -10445,7 +10454,7 @@
 (21年-06月-28日)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $468万
@@ -10453,7 +10462,7 @@
 (21年-06月-22日)</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>F | 242呎 (1房)
 $647万
@@ -10468,7 +10477,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 242呎 (1房)
 $639万
@@ -10476,7 +10485,7 @@
 (21年-06月-22日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $481万
@@ -10484,7 +10493,7 @@
 (21年-10月-08日)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $470万
@@ -10492,7 +10501,7 @@
 (21年-08月-18日)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $485万
@@ -10500,7 +10509,7 @@
 (21年-08月-12日)</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="24" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $500万
@@ -10508,7 +10517,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>F | 242呎 (1房)
 $611万
@@ -10523,7 +10532,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 242呎 (1房)
 $626万
@@ -10531,7 +10540,7 @@
 (21年-06月-22日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $475万
@@ -10539,7 +10548,7 @@
 (21年-06月-29日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $465万
@@ -10547,7 +10556,7 @@
 (21年-06月-22日)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $479万
@@ -10555,7 +10564,7 @@
 (21年-06月-28日)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $461万
@@ -10563,7 +10572,7 @@
 (21年-06月-22日)</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>F | 242呎 (1房)
 $639万
@@ -10578,7 +10587,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 242呎 (1房)
 $638万
@@ -10586,7 +10595,7 @@
 (21年-12月-24日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $470万
@@ -10594,7 +10603,7 @@
 (21年-10月-20日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $456万
@@ -10602,7 +10611,7 @@
 (21年-10月-27日)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $479万
@@ -10610,7 +10619,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="F23" s="24" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $492万
@@ -10618,7 +10627,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>F | 242呎 (1房)
 $635万
@@ -10633,7 +10642,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 242呎 (1房)
 $636万
@@ -10641,7 +10650,7 @@
 (22年-02月-24日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $494万
@@ -10649,7 +10658,7 @@
 (21年-11月-26日)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $483万
@@ -10657,7 +10666,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $478万
@@ -10665,7 +10674,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F24" s="24" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $486万
@@ -10673,7 +10682,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>F | 242呎 (1房)
 $601万
@@ -10688,7 +10697,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 242呎 (1房)
 $623万
@@ -10696,7 +10705,7 @@
 (21年-06月-21日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $471万
@@ -10704,7 +10713,7 @@
 (21年-06月-22日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $451万
@@ -10712,7 +10721,7 @@
 (21年-06月-23日)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $451万
@@ -10720,7 +10729,7 @@
 (21年-06月-29日)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $450万
@@ -10728,7 +10737,7 @@
 (21年-06月-23日)</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>F | 242呎 (1房)
 $596万
@@ -10743,7 +10752,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 242呎 (1房)
 $612万
@@ -10751,7 +10760,7 @@
 (21年-06月-21日)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 -
@@ -10759,7 +10768,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $473万
@@ -10767,7 +10776,7 @@
 (21年-06月-22日)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $443万
@@ -10775,7 +10784,7 @@
 (21年-06月-23日)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $464万
@@ -10783,7 +10792,7 @@
 (21年-06月-16日)</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>F | 242呎 (1房)
 $592万
@@ -10798,7 +10807,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 242呎 (1房)
 $612万
@@ -10806,7 +10815,7 @@
 (21年-07月-02日)</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $488万
@@ -10814,7 +10823,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $444万
@@ -10822,7 +10831,7 @@
 (21年-08月-17日)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $439万
@@ -10830,7 +10839,7 @@
 (21年-10月-04日)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $444万
@@ -10838,7 +10847,7 @@
 (21年-09月-23日)</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="23" t="inlineStr">
         <is>
           <t>F | 242呎 (1房)
 $593万
@@ -10853,7 +10862,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 242呎 (1房)
 $600万
@@ -10861,7 +10870,7 @@
 (21年-06月-10日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 186呎 (开放式)
 $452万
@@ -10869,7 +10878,7 @@
 (21年-10月-11日)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 183呎 (开放式)
 $439万
@@ -10877,7 +10886,7 @@
 (21年-06月-17日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 183呎 (开放式)
 $438万
@@ -10885,7 +10894,7 @@
 (21年-11月-12日)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>E | 186呎 (开放式)
 $428万
@@ -10893,7 +10902,7 @@
 (21年-05月-30日)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>F | 242呎 (1房)
 $581万
